--- a/dimdc/outputs/policy_prd02_adhoc_odcs.xlsx
+++ b/dimdc/outputs/policy_prd02_adhoc_odcs.xlsx
@@ -3042,7 +3042,7 @@
       </c>
       <c r="C19" s="39" t="inlineStr">
         <is>
-          <t>Ad hoc ODCS Excel generated from CSV files in data\raw\policy\20260813095628\prd_02.</t>
+          <t>Ad hoc ODCS Excel generated from data\raw\policy\20260813095628\prd_02.</t>
         </is>
       </c>
     </row>
